--- a/ressources.xlsx
+++ b/ressources.xlsx
@@ -2,16 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
-  <workbookProtection/>
   <bookViews>
-    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
+    <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" xWindow="38280" yWindow="4095" windowWidth="29040" windowHeight="15720" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="ressources" sheetId="1" state="visible" r:id="rId1"/>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="instructions" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
-  <calcPr calcId="124519" fullCalcOnLoad="1"/>
+  <calcPr calcId="0" fullCalcOnLoad="1"/>
 </workbook>
 </file>
 
@@ -29,7 +28,8 @@
     <font>
       <name val="Arial"/>
       <b val="1"/>
-      <color rgb="00FFFFFF"/>
+      <color rgb="FFFFFFFF"/>
+      <sz val="11"/>
     </font>
     <font>
       <name val="Arial"/>
@@ -55,8 +55,8 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="002C5F62"/>
-        <bgColor rgb="002C5F62"/>
+        <fgColor rgb="FF2C5F62"/>
+        <bgColor rgb="FF2C5F62"/>
       </patternFill>
     </fill>
   </fills>
@@ -82,7 +82,7 @@
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
-    <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
+    <cellStyle name="Normal" xfId="0" builtinId="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
@@ -445,20 +445,20 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K8"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <dimension ref="A1:K18"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
-    <col width="22" customWidth="1" min="1" max="1"/>
-    <col width="42" customWidth="1" min="2" max="2"/>
-    <col width="12" customWidth="1" min="3" max="3"/>
-    <col width="20" customWidth="1" min="4" max="4"/>
-    <col width="22" customWidth="1" min="5" max="5"/>
-    <col width="42" customWidth="1" min="6" max="6"/>
-    <col width="16" customWidth="1" min="7" max="7"/>
-    <col width="34" customWidth="1" min="8" max="8"/>
-    <col width="40" customWidth="1" min="9" max="9"/>
-    <col width="10" customWidth="1" min="10" max="10"/>
-    <col width="10" customWidth="1" min="11" max="11"/>
+    <col width="11.81640625" bestFit="1" customWidth="1" min="1" max="1"/>
+    <col width="48.81640625" bestFit="1" customWidth="1" min="2" max="2"/>
+    <col width="7.1796875" bestFit="1" customWidth="1" min="3" max="3"/>
+    <col width="5" bestFit="1" customWidth="1" min="4" max="4"/>
+    <col width="13.36328125" bestFit="1" customWidth="1" min="5" max="5"/>
+    <col width="32.08984375" bestFit="1" customWidth="1" min="6" max="6"/>
+    <col width="13.08984375" bestFit="1" customWidth="1" min="7" max="7"/>
+    <col width="27.08984375" bestFit="1" customWidth="1" min="8" max="8"/>
+    <col width="52.453125" bestFit="1" customWidth="1" min="9" max="9"/>
+    <col width="7.81640625" bestFit="1" customWidth="1" min="10" max="10"/>
+    <col width="6.81640625" bestFit="1" customWidth="1" min="11" max="11"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -574,61 +574,65 @@
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>isere</t>
+          <t>france-alzheimer-paris</t>
         </is>
       </c>
       <c r="B3" s="2" t="inlineStr">
         <is>
-          <t>France Alzheimer Isère</t>
+          <t>France Alzheimer Paris</t>
         </is>
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
-          <t>antenne</t>
+          <t>association</t>
         </is>
       </c>
       <c r="D3" s="2" t="inlineStr">
         <is>
-          <t>Grenoble</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>38 — Isère</t>
+          <t>75 — Paris</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>34 avenue Marcelin Berthelot, 38100 Grenoble</t>
+          <t>169 Rue Saint-Jacques, 75005 Paris</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
         <is>
-          <t>04 76 43 18 19</t>
+          <t>01 45 40 30 91</t>
         </is>
       </c>
       <c r="H3" s="2" t="inlineStr">
         <is>
-          <t>https://www.francealzheimer.org/isere</t>
-        </is>
-      </c>
-      <c r="I3" s="2" t="inlineStr"/>
+          <t>https://www.francealzheimer.org</t>
+        </is>
+      </c>
+      <c r="I3" s="2" t="inlineStr">
+        <is>
+          <t>Gratuit : groupes de parole, entretiens psychologiques individuels, formations des aidants (14h, cycle gratuit sur inscription).</t>
+        </is>
+      </c>
       <c r="J3" s="2" t="n">
-        <v>45.1885</v>
+        <v>48.8407</v>
       </c>
       <c r="K3" s="2" t="n">
-        <v>5.7245</v>
+        <v>2.34</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
         <is>
-          <t>val-de-marne</t>
+          <t>m2a-paris-centre</t>
         </is>
       </c>
       <c r="B4" s="2" t="inlineStr">
         <is>
-          <t>France Alzheimer Val-de-Marne</t>
+          <t>Maison des Aînés et des Aidants (M2A) — Paris Centre</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -638,46 +642,50 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>Nogent-sur-Marne</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>94 — Val-de-Marne</t>
+          <t>75 — Paris</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>4 rue du Maréchal Vaillant, 94130 Nogent-sur-Marne</t>
+          <t>11 Rue de l'École de Médecine, 75006 Paris</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>01 48 72 87 82</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr"/>
+          <t>01 44 07 13 35</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>mailto:contact.centre@m2a.paris</t>
+        </is>
+      </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>Permanences d'accueil dans une dizaine de villes du département.</t>
+          <t>Guichet public gratuit d'accueil, d'écoute et d'orientation. Secteurs : 1er, 2e, 3e, 4e, 5e, 6e.</t>
         </is>
       </c>
       <c r="J4" s="2" t="n">
-        <v>48.8377</v>
+        <v>48.8514</v>
       </c>
       <c r="K4" s="2" t="n">
-        <v>2.483</v>
+        <v>2.3405</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
         <is>
-          <t>seine-saint-denis</t>
+          <t>m2a-paris-nord-est</t>
         </is>
       </c>
       <c r="B5" s="2" t="inlineStr">
         <is>
-          <t>France Alzheimer Seine-Saint-Denis</t>
+          <t>Maison des Aînés et des Aidants (M2A) — Paris Nord-Est</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -687,38 +695,50 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>Le Raincy</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>93 — Seine-Saint-Denis</t>
+          <t>75 — Paris</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>91 avenue de la Résistance, 93340 Le Raincy</t>
-        </is>
-      </c>
-      <c r="G5" s="2" t="inlineStr"/>
-      <c r="H5" s="2" t="inlineStr"/>
-      <c r="I5" s="2" t="inlineStr"/>
+          <t>126 Quai de Jemmapes, 75010 Paris</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>01 40 40 27 80</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>mailto:contact.nordest@m2a.paris</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>Guichet public gratuit d'accueil, d'écoute et d'orientation. Secteurs : 9e, 10e, 19e.</t>
+        </is>
+      </c>
       <c r="J5" s="2" t="n">
-        <v>48.8933</v>
+        <v>48.8815</v>
       </c>
       <c r="K5" s="2" t="n">
-        <v>2.515</v>
+        <v>2.3695</v>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
         <is>
-          <t>aisne</t>
+          <t>m2a-paris-est</t>
         </is>
       </c>
       <c r="B6" s="2" t="inlineStr">
         <is>
-          <t>France Alzheimer Aisne</t>
+          <t>Maison des Aînés et des Aidants (M2A) — Paris Est</t>
         </is>
       </c>
       <c r="C6" s="2" t="inlineStr">
@@ -728,42 +748,50 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>Soissons</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>02 — Aisne</t>
+          <t>75 — Paris</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>35 boulevard Jeanne d'Arc, immeuble Royaumont, 02200 Soissons</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr"/>
+          <t>20 Rue du Sergent Bauchat, 75012 Paris</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>01 58 70 09 10</t>
+        </is>
+      </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>mailto:aisnealzheimer@gmail.com</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr"/>
+          <t>mailto:contact.est@m2a.paris</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>Guichet public gratuit d'accueil, d'écoute et d'orientation. Secteurs : 11e, 12e, 20e.</t>
+        </is>
+      </c>
       <c r="J6" s="2" t="n">
-        <v>49.3793</v>
+        <v>48.8395</v>
       </c>
       <c r="K6" s="2" t="n">
-        <v>3.3236</v>
+        <v>2.3925</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
         <is>
-          <t>seine-et-marne</t>
+          <t>m2a-paris-sud</t>
         </is>
       </c>
       <c r="B7" s="2" t="inlineStr">
         <is>
-          <t>France Alzheimer Seine-et-Marne</t>
+          <t>Maison des Aînés et des Aidants (M2A) — Paris Sud</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -773,80 +801,562 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>Saint-Fargeau-Ponthierry</t>
+          <t>Paris</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>77 — Seine-et-Marne</t>
+          <t>75 — Paris</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>77310 Saint-Fargeau-Ponthierry (siège)</t>
-        </is>
-      </c>
-      <c r="G7" s="2" t="inlineStr"/>
-      <c r="H7" s="2" t="inlineStr"/>
-      <c r="I7" s="2" t="inlineStr"/>
+          <t>58A Rue du Dessous des Berges, 75013 Paris</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>01 45 88 21 09</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>mailto:contact.sud@m2a.paris</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>Guichet public gratuit d'accueil, d'écoute et d'orientation. Secteurs : 13e, 14e.</t>
+        </is>
+      </c>
       <c r="J7" s="2" t="n">
-        <v>48.545</v>
+        <v>48.829</v>
       </c>
       <c r="K7" s="2" t="n">
-        <v>2.6033</v>
+        <v>2.3735</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
         <is>
-          <t>exemple-club-cafe-memoire</t>
+          <t>m2a-paris-ouest</t>
         </is>
       </c>
       <c r="B8" s="2" t="inlineStr">
         <is>
-          <t>Exemple : Café mémoire de Villeneuve</t>
+          <t>Maison des Aînés et des Aidants (M2A) — Paris Ouest</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>antenne</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>75 — Paris</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>3 Place Adolphe Chérioux, 75015 Paris</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>01 44 19 61 60</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>mailto:contact.ouest@m2a.paris</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>Guichet public gratuit d'accueil, d'écoute et d'orientation. Secteurs : 7e, 15e, 16e.</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="n">
+        <v>48.8391</v>
+      </c>
+      <c r="K8" s="2" t="n">
+        <v>2.2989</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="2" t="inlineStr">
+        <is>
+          <t>m2a-paris-nord-ouest</t>
+        </is>
+      </c>
+      <c r="B9" s="2" t="inlineStr">
+        <is>
+          <t>Maison des Aînés et des Aidants (M2A) — Paris Nord-Ouest</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>antenne</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>75 — Paris</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>56 Rue Ordener, 75018 Paris</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>01 53 11 18 18</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>mailto:contact.nordouest@m2a.paris</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>Guichet public gratuit d'accueil, d'écoute et d'orientation. Secteurs : 8e, 17e, 18e.</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="n">
+        <v>48.893</v>
+      </c>
+      <c r="K9" s="2" t="n">
+        <v>2.3538</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="2" t="inlineStr">
+        <is>
+          <t>pfr-delta-7</t>
+        </is>
+      </c>
+      <c r="B10" s="2" t="inlineStr">
+        <is>
+          <t>Plateforme d'Accompagnement et de Répit — Delta 7 (Paris Ouest &amp; Nord)</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>75 — Paris</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>106 Avenue Émile Zola, 75015 Paris</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>01 40 40 00 00</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="n"/>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>Gratuit, financé par l'ARS : temps de répit, soutien psychologique, activités partagées. Secteurs : 8e, 9e, 10e, 15e, 17e, 18e, 19e.</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="n">
+        <v>48.8465</v>
+      </c>
+      <c r="K10" s="2" t="n">
+        <v>2.2838</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="2" t="inlineStr">
+        <is>
+          <t>pfr-le-relais</t>
+        </is>
+      </c>
+      <c r="B11" s="2" t="inlineStr">
+        <is>
+          <t>Plateforme d'Accompagnement et de Répit — Le Relais (Fondation Œuvre de la Croix Saint-Simon, Paris Est)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>75 — Paris</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>10 Rue de Santerre, 75012 Paris</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>01 56 27 06 90</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="n"/>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>Gratuit, financé par l'ARS : temps de répit, soutien psychologique, activités partagées. Secteurs : 11e, 12e, 20e.</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="n">
+        <v>48.8405</v>
+      </c>
+      <c r="K11" s="2" t="n">
+        <v>2.391</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="2" t="inlineStr">
+        <is>
+          <t>pfr-maison-repit-jeanne-garnier</t>
+        </is>
+      </c>
+      <c r="B12" s="2" t="inlineStr">
+        <is>
+          <t>Plateforme d'Accompagnement et de Répit — Maison de Répit / Établissements Jeanne Garnier (Paris Centre/Sud)</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>75 — Paris</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>68 Rue des Plantes, 75014 Paris</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="n"/>
+      <c r="H12" s="2" t="n"/>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>Gratuit, financé par l'ARS : temps de répit, soutien psychologique, activités partagées. Secteurs : 5e, 6e, 7e, 13e, 14e.</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="n">
+        <v>48.8285</v>
+      </c>
+      <c r="K12" s="2" t="n">
+        <v>2.3195</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="2" t="inlineStr">
+        <is>
+          <t>club-aidants-joseph-weill-ose</t>
+        </is>
+      </c>
+      <c r="B13" s="2" t="inlineStr">
+        <is>
+          <t>Club des Aidants Joseph Weill — OSE</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
           <t>club</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>Villeneuve-sur-Exemple</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>XX — Nom du département</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>12 rue de l'Exemple, 00000 Villeneuve-sur-Exemple</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>01 23 45 67 89</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>https://exemple-cafe-memoire.fr</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>Ligne d'exemple : remplacez ou dupliquez pour ajouter un vrai club, puis supprimez cette ligne si besoin.</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="n">
-        <v>46</v>
-      </c>
-      <c r="K8" s="2" t="n">
-        <v>2</v>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>75 — Paris</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>5 Rue Firmin Gémier, 75018 Paris</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="n"/>
+      <c r="H13" s="2" t="n"/>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>Club d'aidants gratuit. Secteur : Paris Nord-Est / 18e.</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="n">
+        <v>48.8965</v>
+      </c>
+      <c r="K13" s="2" t="n">
+        <v>2.3605</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="2" t="inlineStr">
+        <is>
+          <t>alzheimer-ecoute</t>
+        </is>
+      </c>
+      <c r="B14" s="2" t="inlineStr">
+        <is>
+          <t>Alzheimer Écoute (France Alzheimer)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>75 — Paris</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="n"/>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>0 811 112 112</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>https://www.francealzheimer.org</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>Ligne d'écoute nationale gratuite (prix d'un appel local), anonyme, tous les jours de 20h à 22h. Sans adresse physique à Paris.</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="n">
+        <v>48.8566</v>
+      </c>
+      <c r="K14" s="2" t="n">
+        <v>2.3522</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="2" t="inlineStr">
+        <is>
+          <t>avec-les-aidants-ligne</t>
+        </is>
+      </c>
+      <c r="B15" s="2" t="inlineStr">
+        <is>
+          <t>Avec les Aidants (Ligne Nationale)</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>association</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>75 — Paris</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="n"/>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>01 84 72 94 72</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="n"/>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>Plateforme téléphonique nationale gratuite (numéro non surtaxé) d'aide, d'orientation sociale et de soutien moral. Sans adresse physique à Paris.</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="n">
+        <v>48.8566</v>
+      </c>
+      <c r="K15" s="2" t="n">
+        <v>2.3522</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="2" t="inlineStr">
+        <is>
+          <t>seniors-autonomie-paris</t>
+        </is>
+      </c>
+      <c r="B16" s="2" t="inlineStr">
+        <is>
+          <t>Seniors / Autonomie — Ville de Paris</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>antenne</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>75 — Paris</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="n"/>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>39 75</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="n"/>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>Service téléphonique gratuit (prix d'un appel local) d'information sur le maintien à domicile, les aides sociales et les démarches sanitaires. Sans adresse physique dédiée.</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="n">
+        <v>48.8566</v>
+      </c>
+      <c r="K16" s="2" t="n">
+        <v>2.3522</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="2" t="inlineStr">
+        <is>
+          <t>bistrots-memoire-paris</t>
+        </is>
+      </c>
+      <c r="B17" s="2" t="inlineStr">
+        <is>
+          <t>Les Bistrots Mémoire (Réseau Bistro Mémoire France)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>club</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>75 — Paris</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="n"/>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>01 45 40 30 91</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="n"/>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>Rencontres conviviales mensuelles et gratuites (entrée libre) entre aidants, malades et professionnels, dans divers cafés parisiens. Lieux variables ; contact via France Alzheimer Paris.</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="n">
+        <v>48.8407</v>
+      </c>
+      <c r="K17" s="2" t="n">
+        <v>2.34</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="2" t="inlineStr">
+        <is>
+          <t>cafe-des-aidants-paris</t>
+        </is>
+      </c>
+      <c r="B18" s="2" t="inlineStr">
+        <is>
+          <t>Café des Aidants (Association Française des Aidants)</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>club</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>Paris</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>75 — Paris</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="n"/>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>01 45 26 22 99</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="n"/>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>Ateliers et débats gratuits animés par un psychologue et un travailleur social. Lieux variables selon les sessions ; contacter pour connaître les adresses actives à Paris.</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="n">
+        <v>48.8566</v>
+      </c>
+      <c r="K18" s="2" t="n">
+        <v>2.3522</v>
       </c>
     </row>
   </sheetData>
@@ -861,13 +1371,13 @@
     <pageSetUpPr/>
   </sheetPr>
   <dimension ref="A1:B25"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="22" customWidth="1" min="1" max="1"/>
     <col width="90" customWidth="1" min="2" max="2"/>
   </cols>
   <sheetData>
-    <row r="1">
+    <row r="1" ht="16.5" customHeight="1">
       <c r="A1" s="3" t="inlineStr">
         <is>
           <t>Comment ajouter une ressource</t>
@@ -875,7 +1385,7 @@
       </c>
     </row>
     <row r="2">
-      <c r="A2" s="2" t="inlineStr"/>
+      <c r="A2" s="2" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -913,9 +1423,9 @@
       </c>
     </row>
     <row r="8">
-      <c r="A8" s="2" t="inlineStr"/>
-    </row>
-    <row r="9">
+      <c r="A8" s="2" t="n"/>
+    </row>
+    <row r="9" ht="16.5" customHeight="1">
       <c r="A9" s="3" t="inlineStr">
         <is>
           <t>Détail des colonnes</t>
@@ -1043,9 +1553,9 @@
       </c>
     </row>
     <row r="20">
-      <c r="A20" s="2" t="inlineStr"/>
-    </row>
-    <row r="21">
+      <c r="A20" s="2" t="n"/>
+    </row>
+    <row r="21" ht="16.5" customHeight="1">
       <c r="A21" s="3" t="inlineStr">
         <is>
           <t>Pour supprimer une ressource</t>
@@ -1060,9 +1570,9 @@
       </c>
     </row>
     <row r="23">
-      <c r="A23" s="2" t="inlineStr"/>
-    </row>
-    <row r="24">
+      <c r="A23" s="2" t="n"/>
+    </row>
+    <row r="24" ht="16.5" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
           <t>Important</t>
